--- a/AAII_Financials/Yearly/MLCI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MLCI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>MLCI</t>
   </si>
@@ -1623,7 +1623,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>20200</v>
+        <v>19800</v>
       </c>
       <c r="E43" s="3">
         <v>40200</v>
@@ -1713,7 +1713,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>165100</v>
+        <v>164800</v>
       </c>
       <c r="E46" s="3">
         <v>142500</v>
@@ -1893,7 +1893,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>276700</v>
+        <v>277100</v>
       </c>
       <c r="E52" s="3">
         <v>262200</v>
@@ -2011,10 +2011,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15600</v>
-      </c>
-      <c r="E57" s="3">
-        <v>5100</v>
+        <v>6500</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F57" s="3">
         <v>13100</v>
@@ -2041,10 +2041,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5500</v>
+        <v>6900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="F58" s="3">
         <v>1300</v>
@@ -2101,10 +2101,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>37000</v>
+        <v>38300</v>
       </c>
       <c r="E60" s="3">
-        <v>18600</v>
+        <v>23800</v>
       </c>
       <c r="F60" s="3">
         <v>47100</v>
@@ -2131,10 +2131,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E61" s="3">
         <v>89800</v>
-      </c>
-      <c r="E61" s="3">
-        <v>95000</v>
       </c>
       <c r="F61" s="3">
         <v>74900</v>
